--- a/data/trans_orig/RUIDO_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan el ruido en su municipio o lugar de residencia en 2023</t>
+          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan el ruido en su municipio o lugar de residencia en 2023 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>18397</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>21751</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41883</t>
+          <t>42645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28335</t>
+          <t>26788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22412</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42677</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67292</t>
+          <t>67163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96342</t>
+          <t>96547</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59367</t>
+          <t>58733</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80105</t>
+          <t>80022</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>131570</t>
+          <t>134906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>167225</t>
+          <t>168637</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23991</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46367</t>
+          <t>48200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>16748</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32056</t>
+          <t>31413</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46053</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72525</t>
+          <t>73234</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26484</t>
+          <t>25783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47907</t>
+          <t>47237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19858</t>
+          <t>19236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34702</t>
+          <t>34782</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50371</t>
+          <t>50013</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76117</t>
+          <t>75184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>12681</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40275</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>19156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50159</t>
+          <t>52455</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27569</t>
+          <t>27107</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27194</t>
+          <t>26021</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48338</t>
+          <t>47293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70166</t>
+          <t>71157</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>98946</t>
+          <t>99626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54612</t>
+          <t>53709</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73998</t>
+          <t>73426</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131354</t>
+          <t>131084</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>166776</t>
+          <t>166148</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,57%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29274</t>
+          <t>28570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50426</t>
+          <t>50574</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35576</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52024</t>
+          <t>52638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78994</t>
+          <t>79753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12322</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27974</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>18766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33263</t>
+          <t>33596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33656</t>
+          <t>34165</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55125</t>
+          <t>55178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13340</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17717</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28997</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49042</t>
+          <t>49391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>13494</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23764</t>
+          <t>24633</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45528</t>
+          <t>45944</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69437</t>
+          <t>69908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67965</t>
+          <t>68135</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94654</t>
+          <t>93177</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>85655</t>
+          <t>85060</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113643</t>
+          <t>113424</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19075</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38923</t>
+          <t>38772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6896</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>16035</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28472</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50045</t>
+          <t>51179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>35303</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30672</t>
+          <t>30483</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50563</t>
+          <t>50338</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -2776,82 +2776,82 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>32377</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>70632</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>17,18%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>24715</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>8198</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>47355</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>72526</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>32667</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>68953</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>16,77%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>24715</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>6480</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>46522</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>72526</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>35641</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104894</t>
+          <t>104191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91242</t>
+          <t>90441</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129071</t>
+          <t>129482</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>145697</t>
+          <t>146493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>424958</t>
+          <t>423962</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>246216</t>
+          <t>248034</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>656375</t>
+          <t>661966</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>135323</t>
+          <t>133940</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>179688</t>
+          <t>180912</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>41884</t>
+          <t>39871</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>195997</t>
+          <t>193836</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>127406</t>
+          <t>129964</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>354134</t>
+          <t>354170</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43115</t>
+          <t>42230</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70090</t>
+          <t>71789</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>12218</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69063</t>
+          <t>67656</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46609</t>
+          <t>45536</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>128165</t>
+          <t>127154</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32685</t>
+          <t>33667</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57576</t>
+          <t>58907</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57370</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>34947</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>103573</t>
+          <t>103391</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19232</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36164</t>
+          <t>35820</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27322</t>
+          <t>27805</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46709</t>
+          <t>46439</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>65960</t>
+          <t>66658</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93416</t>
+          <t>93754</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>109369</t>
+          <t>108282</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>136368</t>
+          <t>136452</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>181602</t>
+          <t>182131</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>220980</t>
+          <t>222324</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,98%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48662</t>
+          <t>48871</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74978</t>
+          <t>74887</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>64998</t>
+          <t>64323</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89435</t>
+          <t>87172</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>119463</t>
+          <t>119717</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>156362</t>
+          <t>154441</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30093</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28391</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>46618</t>
+          <t>47047</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>43816</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>69384</t>
+          <t>69381</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>29312</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>25868</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42710</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43040</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>65524</t>
+          <t>67209</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>38856</t>
+          <t>40678</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>51516</t>
+          <t>53294</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>42440</t>
+          <t>41797</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>88630</t>
+          <t>87556</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>36579</t>
+          <t>38274</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>101383</t>
+          <t>99663</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>132663</t>
+          <t>130865</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>119366</t>
+          <t>117038</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>160868</t>
+          <t>159286</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>25386</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>72395</t>
+          <t>73002</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>101736</t>
+          <t>102069</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>83538</t>
+          <t>83465</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>120554</t>
+          <t>118285</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>28864</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>47292</t>
+          <t>48966</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>33669</t>
+          <t>33610</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>57948</t>
+          <t>56430</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>24702</t>
+          <t>24182</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>39925</t>
+          <t>39219</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>65237</t>
+          <t>64532</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>47677</t>
+          <t>47476</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>81667</t>
+          <t>76899</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>95850</t>
+          <t>94812</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>159537</t>
+          <t>155737</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>76434</t>
+          <t>75895</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>150746</t>
+          <t>147400</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,17 +4887,17 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>241017</t>
+          <t>241018</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>188902</t>
+          <t>187630</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>285790</t>
+          <t>286300</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>246791</t>
+          <t>244423</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>312296</t>
+          <t>307769</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>428951</t>
+          <t>430263</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>908783</t>
+          <t>890769</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>693214</t>
+          <t>693757</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1326194</t>
+          <t>1311787</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>437020</t>
+          <t>442322</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>513362</t>
+          <t>515940</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>264010</t>
+          <t>269885</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>509365</t>
+          <t>503698</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>682979</t>
+          <t>689759</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>998838</t>
+          <t>996632</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>158774</t>
+          <t>159304</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>209537</t>
+          <t>210436</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>110663</t>
+          <t>108848</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>208434</t>
+          <t>208015</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>272925</t>
+          <t>273182</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>400829</t>
+          <t>401180</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>131854</t>
+          <t>132398</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>179189</t>
+          <t>178718</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>113205</t>
+          <t>118158</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>217472</t>
+          <t>217774</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>259599</t>
+          <t>255092</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>380618</t>
+          <t>378376</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2697728</t>
+          <t>2697729</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2697728</t>
+          <t>2697729</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2697728</t>
+          <t>2697729</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">

--- a/data/trans_orig/RUIDO_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28618</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>14532</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30129</t>
+          <t>32840</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21751</t>
+          <t>23241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42645</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>14549</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26788</t>
+          <t>28629</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>25882</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27042</t>
+          <t>30850</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>21225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40576</t>
+          <t>44238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>82132</t>
+          <t>87156</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>73463</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96547</t>
+          <t>102507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69570</t>
+          <t>73634</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58733</t>
+          <t>63351</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80022</t>
+          <t>85647</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>151703</t>
+          <t>160790</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>134906</t>
+          <t>143124</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>168637</t>
+          <t>178150</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35279</t>
+          <t>35961</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25955</t>
+          <t>25281</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48200</t>
+          <t>47445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23696</t>
+          <t>26380</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16748</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31413</t>
+          <t>35382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58975</t>
+          <t>62341</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46171</t>
+          <t>49410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73234</t>
+          <t>75804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>35782</t>
+          <t>39119</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>29064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47237</t>
+          <t>52219</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>28343</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19236</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34782</t>
+          <t>37689</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>62124</t>
+          <t>67462</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50013</t>
+          <t>54301</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75184</t>
+          <t>81312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>183375</t>
+          <t>195093</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>183375</t>
+          <t>195093</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183375</t>
+          <t>195093</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>146598</t>
+          <t>159190</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>146598</t>
+          <t>159190</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146598</t>
+          <t>159190</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>329973</t>
+          <t>354282</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>329973</t>
+          <t>354282</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>329973</t>
+          <t>354282</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22358</t>
+          <t>21149</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35969</t>
+          <t>34770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>13559</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34080</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>23258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52455</t>
+          <t>49323</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>17569</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27107</t>
+          <t>27466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18857</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>14667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>29356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>35815</t>
+          <t>38537</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26021</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47293</t>
+          <t>50809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85339</t>
+          <t>90122</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71157</t>
+          <t>74383</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99626</t>
+          <t>103687</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64013</t>
+          <t>68651</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53709</t>
+          <t>57779</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73426</t>
+          <t>80659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>149353</t>
+          <t>158773</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131084</t>
+          <t>139967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>166148</t>
+          <t>178898</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38813</t>
+          <t>40611</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>30145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50574</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>28343</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>65544</t>
+          <t>68955</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52638</t>
+          <t>55027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79753</t>
+          <t>84268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27122</t>
+          <t>29517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25038</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18766</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33596</t>
+          <t>38163</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>43774</t>
+          <t>48428</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34165</t>
+          <t>37885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55178</t>
+          <t>60734</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>182204</t>
+          <t>189544</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>182204</t>
+          <t>189544</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>182204</t>
+          <t>189544</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>146362</t>
+          <t>159856</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>146362</t>
+          <t>159856</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>146362</t>
+          <t>159856</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>328566</t>
+          <t>349400</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>328566</t>
+          <t>349400</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>328566</t>
+          <t>349400</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>12882</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38304</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27837</t>
+          <t>34653</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49391</t>
+          <t>59884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24633</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>56566</t>
+          <t>68360</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45944</t>
+          <t>55182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69908</t>
+          <t>82988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>80714</t>
+          <t>88003</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68135</t>
+          <t>72084</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93177</t>
+          <t>101216</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>21464</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>16005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24784</t>
+          <t>28531</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>99309</t>
+          <t>109467</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>85060</t>
+          <t>92441</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113424</t>
+          <t>124935</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>21885</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38772</t>
+          <t>43578</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16035</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>38349</t>
+          <t>42401</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28189</t>
+          <t>32384</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51179</t>
+          <t>55862</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25664</t>
+          <t>28221</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35303</t>
+          <t>38797</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19659</t>
+          <t>21424</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>39546</t>
+          <t>43748</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>34193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50338</t>
+          <t>55891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>176687</t>
+          <t>198132</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>176687</t>
+          <t>198132</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>176687</t>
+          <t>198132</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66514</t>
+          <t>75753</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>66514</t>
+          <t>75753</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66514</t>
+          <t>75753</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>243201</t>
+          <t>273885</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>243201</t>
+          <t>273885</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>243201</t>
+          <t>273885</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>47811</t>
+          <t>50732</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32377</t>
+          <t>35643</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70632</t>
+          <t>72431</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24715</t>
+          <t>29555</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>21259</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47355</t>
+          <t>40291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>72526</t>
+          <t>80287</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>61927</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104191</t>
+          <t>102629</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>108621</t>
+          <t>119916</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90441</t>
+          <t>100534</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129482</t>
+          <t>140540</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>295496</t>
+          <t>100054</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>146493</t>
+          <t>86335</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>423962</t>
+          <t>113816</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>404118</t>
+          <t>219970</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248034</t>
+          <t>196145</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>661966</t>
+          <t>245190</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>155476</t>
+          <t>161107</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>133940</t>
+          <t>141231</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>180912</t>
+          <t>182206</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>110541</t>
+          <t>119657</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39871</t>
+          <t>106172</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>193836</t>
+          <t>135689</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>266017</t>
+          <t>280763</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>129964</t>
+          <t>258033</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>354170</t>
+          <t>309216</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>55150</t>
+          <t>64207</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42230</t>
+          <t>50344</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>71789</t>
+          <t>80878</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>37373</t>
+          <t>40771</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>30210</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67656</t>
+          <t>53132</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>92523</t>
+          <t>104978</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45536</t>
+          <t>84984</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>127154</t>
+          <t>124821</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>44069</t>
+          <t>48825</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>37164</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58907</t>
+          <t>64533</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>30308</t>
+          <t>34560</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56769</t>
+          <t>45616</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>74378</t>
+          <t>83385</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34947</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>102851</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>411128</t>
+          <t>444788</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>411128</t>
+          <t>444788</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>411128</t>
+          <t>444788</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>498433</t>
+          <t>324597</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>498433</t>
+          <t>324597</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>498433</t>
+          <t>324597</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>909561</t>
+          <t>769384</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>909561</t>
+          <t>769384</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>909561</t>
+          <t>769384</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>27194</t>
+          <t>29570</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20031</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35820</t>
+          <t>40060</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>35898</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27805</t>
+          <t>29835</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46439</t>
+          <t>49309</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>79127</t>
+          <t>103238</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>66658</t>
+          <t>87492</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93754</t>
+          <t>119385</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>121282</t>
+          <t>140712</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>108282</t>
+          <t>124797</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>136452</t>
+          <t>154807</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>200409</t>
+          <t>243950</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>182131</t>
+          <t>223110</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>222324</t>
+          <t>266401</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>61207</t>
+          <t>66711</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48871</t>
+          <t>53814</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74887</t>
+          <t>82690</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>76245</t>
+          <t>83436</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>64323</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>87172</t>
+          <t>97059</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>137452</t>
+          <t>150148</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>132665</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>154441</t>
+          <t>170713</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>19835</t>
+          <t>22680</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>36455</t>
+          <t>40844</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>31396</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>47047</t>
+          <t>51913</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>56289</t>
+          <t>63525</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>44272</t>
+          <t>51773</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>69381</t>
+          <t>79143</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29312</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>33506</t>
+          <t>38963</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>30320</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>50468</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,17 +3975,17 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>53506</t>
+          <t>61773</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43423</t>
+          <t>50794</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>67209</t>
+          <t>75097</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>188872</t>
+          <t>224390</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>188872</t>
+          <t>224390</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>188872</t>
+          <t>224390</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>294682</t>
+          <t>333526</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>294682</t>
+          <t>333526</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>294682</t>
+          <t>333526</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>483554</t>
+          <t>557916</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>483554</t>
+          <t>557916</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>483554</t>
+          <t>557916</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21147</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>40678</t>
+          <t>35711</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>37808</t>
+          <t>39939</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>53294</t>
+          <t>57266</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>58285</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>41797</t>
+          <t>40951</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>87556</t>
+          <t>83789</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>24954</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>37933</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>115939</t>
+          <t>134386</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>99663</t>
+          <t>117079</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>130865</t>
+          <t>153419</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>138396</t>
+          <t>159340</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>117038</t>
+          <t>139036</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>159286</t>
+          <t>182795</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25386</t>
+          <t>24558</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>86882</t>
+          <t>91865</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>73002</t>
+          <t>76554</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>107860</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>100356</t>
+          <t>105406</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>83465</t>
+          <t>88382</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>118285</t>
+          <t>124188</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,22 +4509,22 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>37338</t>
+          <t>41650</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>48966</t>
+          <t>53717</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>43500</t>
+          <t>49056</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>33610</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>56430</t>
+          <t>65628</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>26373</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>50928</t>
+          <t>57540</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>45682</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>64532</t>
+          <t>72963</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>61666</t>
+          <t>70790</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>56009</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>76899</t>
+          <t>90969</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>73979</t>
+          <t>77497</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>73979</t>
+          <t>77497</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>73979</t>
+          <t>77497</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>328895</t>
+          <t>365381</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>328895</t>
+          <t>365381</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>328895</t>
+          <t>365381</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>402874</t>
+          <t>442878</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>402874</t>
+          <t>442878</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>402874</t>
+          <t>442878</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>121992</t>
+          <t>122139</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>94812</t>
+          <t>96142</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>155737</t>
+          <t>152551</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>119025</t>
+          <t>132409</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>75895</t>
+          <t>111888</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>147400</t>
+          <t>155424</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>241018</t>
+          <t>254548</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>187630</t>
+          <t>218023</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>286300</t>
+          <t>290728</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>278112</t>
+          <t>326821</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>244423</t>
+          <t>296330</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>307769</t>
+          <t>361027</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>584235</t>
+          <t>434186</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>430263</t>
+          <t>402359</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>890769</t>
+          <t>463720</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>862347</t>
+          <t>761007</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>693757</t>
+          <t>715866</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1311787</t>
+          <t>805401</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>478343</t>
+          <t>506640</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>442322</t>
+          <t>466690</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>515940</t>
+          <t>541527</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>425847</t>
+          <t>458707</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>269885</t>
+          <t>429399</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>503698</t>
+          <t>489215</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>904190</t>
+          <t>965347</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>689759</t>
+          <t>913595</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>996632</t>
+          <t>1018137</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>182808</t>
+          <t>201524</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>159304</t>
+          <t>176273</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>210436</t>
+          <t>232876</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>172372</t>
+          <t>189732</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>108848</t>
+          <t>167013</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>208015</t>
+          <t>213043</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>355180</t>
+          <t>391256</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>273182</t>
+          <t>357862</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>401180</t>
+          <t>427423</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>154989</t>
+          <t>172319</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>132398</t>
+          <t>146785</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>178718</t>
+          <t>198918</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>180005</t>
+          <t>203268</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>118158</t>
+          <t>179996</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>217774</t>
+          <t>229991</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>334994</t>
+          <t>375587</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>255092</t>
+          <t>341510</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>378376</t>
+          <t>410334</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1216245</t>
+          <t>1329443</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1216245</t>
+          <t>1329443</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1216245</t>
+          <t>1329443</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1481484</t>
+          <t>1418302</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1481484</t>
+          <t>1418302</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1481484</t>
+          <t>1418302</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2697729</t>
+          <t>2747745</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2697729</t>
+          <t>2747745</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2697729</t>
+          <t>2747745</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
